--- a/wvc/512x512/saidaNLM.xlsx
+++ b/wvc/512x512/saidaNLM.xlsx
@@ -467,22 +467,22 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.6775940817655202</v>
+        <v>0.8861171489674664</v>
       </c>
       <c r="B2" t="n">
-        <v>24.22939985201209</v>
+        <v>34.17020531816788</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7231070617310263</v>
+        <v>0.899598669610324</v>
       </c>
       <c r="D2" t="n">
-        <v>25.81959582074187</v>
+        <v>34.9320324142986</v>
       </c>
       <c r="E2" t="n">
-        <v>16.55233860015869</v>
+        <v>15.87304401397705</v>
       </c>
       <c r="F2" t="n">
-        <v>222.7099466323853</v>
+        <v>232.2781782150269</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -492,22 +492,22 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.7223769923759555</v>
+        <v>0.9161768790919432</v>
       </c>
       <c r="B3" t="n">
-        <v>23.23471838510435</v>
+        <v>33.01541985761661</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7601901824461939</v>
+        <v>0.9274434035576725</v>
       </c>
       <c r="D3" t="n">
-        <v>24.57939741102874</v>
+        <v>33.9425523544006</v>
       </c>
       <c r="E3" t="n">
-        <v>8.221808195114136</v>
+        <v>8.003338575363159</v>
       </c>
       <c r="F3" t="n">
-        <v>214.0236067771912</v>
+        <v>230.4835765361786</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -517,22 +517,22 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.6639230386354218</v>
+        <v>0.9024340770278761</v>
       </c>
       <c r="B4" t="n">
-        <v>23.02309310582744</v>
+        <v>33.65503386059147</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7071364461367107</v>
+        <v>0.90959852040274</v>
       </c>
       <c r="D4" t="n">
-        <v>24.48293455124756</v>
+        <v>34.54771115324892</v>
       </c>
       <c r="E4" t="n">
-        <v>8.328837633132935</v>
+        <v>8.001450538635254</v>
       </c>
       <c r="F4" t="n">
-        <v>216.2712178230286</v>
+        <v>232.452130317688</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -542,22 +542,22 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.7383371785606795</v>
+        <v>0.8871625270124264</v>
       </c>
       <c r="B5" t="n">
-        <v>21.53581509397067</v>
+        <v>31.3251095231007</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7546350561439952</v>
+        <v>0.9015753653971627</v>
       </c>
       <c r="D5" t="n">
-        <v>22.33376921145384</v>
+        <v>31.8994551632011</v>
       </c>
       <c r="E5" t="n">
-        <v>8.515220642089844</v>
+        <v>8.058779954910278</v>
       </c>
       <c r="F5" t="n">
-        <v>215.9784536361694</v>
+        <v>230.0810015201569</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -567,22 +567,22 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.6731118365638312</v>
+        <v>0.8166928700170565</v>
       </c>
       <c r="B6" t="n">
-        <v>22.28208103130565</v>
+        <v>31.07567769971851</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6987469337563829</v>
+        <v>0.8530732156657302</v>
       </c>
       <c r="D6" t="n">
-        <v>23.2376428813479</v>
+        <v>31.91355858731364</v>
       </c>
       <c r="E6" t="n">
-        <v>8.255101203918457</v>
+        <v>8.080157995223999</v>
       </c>
       <c r="F6" t="n">
-        <v>215.2891030311584</v>
+        <v>233.0340375900269</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -592,22 +592,22 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.6927047317654622</v>
+        <v>0.8921824556736816</v>
       </c>
       <c r="B7" t="n">
-        <v>23.21697157161676</v>
+        <v>32.18736637466782</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7306457632233702</v>
+        <v>0.9131371485799739</v>
       </c>
       <c r="D7" t="n">
-        <v>24.4821697309207</v>
+        <v>33.19145271604151</v>
       </c>
       <c r="E7" t="n">
-        <v>8.223755598068237</v>
+        <v>7.987625122070312</v>
       </c>
       <c r="F7" t="n">
-        <v>214.0920946598053</v>
+        <v>230.6567084789276</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -617,22 +617,22 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.7767930989506446</v>
+        <v>0.8893476211544213</v>
       </c>
       <c r="B8" t="n">
-        <v>22.58218041804603</v>
+        <v>28.97553044744797</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7805963170950482</v>
+        <v>0.8962880393038596</v>
       </c>
       <c r="D8" t="n">
-        <v>22.93799368020267</v>
+        <v>29.27686659475171</v>
       </c>
       <c r="E8" t="n">
-        <v>8.261344432830811</v>
+        <v>8.022081613540649</v>
       </c>
       <c r="F8" t="n">
-        <v>213.9648358821869</v>
+        <v>234.1394703388214</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -642,22 +642,22 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.71516053519349</v>
+        <v>0.8622538169539372</v>
       </c>
       <c r="B9" t="n">
-        <v>22.75413363260093</v>
+        <v>30.01820503466334</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7305433380351294</v>
+        <v>0.8743414680027068</v>
       </c>
       <c r="D9" t="n">
-        <v>23.45321857305606</v>
+        <v>30.45750703294904</v>
       </c>
       <c r="E9" t="n">
-        <v>8.17845630645752</v>
+        <v>8.141217231750488</v>
       </c>
       <c r="F9" t="n">
-        <v>215.6296834945679</v>
+        <v>233.3003814220428</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -667,22 +667,22 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.7127077909786521</v>
+        <v>0.8202222150999812</v>
       </c>
       <c r="B10" t="n">
-        <v>21.87592166249703</v>
+        <v>28.65938930181975</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7172444933908263</v>
+        <v>0.8407044534729777</v>
       </c>
       <c r="D10" t="n">
-        <v>22.30924033098308</v>
+        <v>28.79125069467843</v>
       </c>
       <c r="E10" t="n">
-        <v>8.194105625152588</v>
+        <v>8.19125771522522</v>
       </c>
       <c r="F10" t="n">
-        <v>215.5119795799255</v>
+        <v>233.1440522670746</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -692,22 +692,22 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.7496488072097098</v>
+        <v>0.8420104046041545</v>
       </c>
       <c r="B11" t="n">
-        <v>21.89119752695352</v>
+        <v>29.60408860275721</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7640264084206675</v>
+        <v>0.8725589575925421</v>
       </c>
       <c r="D11" t="n">
-        <v>22.5272671576834</v>
+        <v>30.37175766672542</v>
       </c>
       <c r="E11" t="n">
-        <v>8.809779167175293</v>
+        <v>8.010554313659668</v>
       </c>
       <c r="F11" t="n">
-        <v>213.896924495697</v>
+        <v>231.0029127597809</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -717,22 +717,22 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.743528071458701</v>
+        <v>0.863208658876318</v>
       </c>
       <c r="B12" t="n">
-        <v>21.82496993209351</v>
+        <v>29.54340500943817</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7529054138227136</v>
+        <v>0.8789693593824283</v>
       </c>
       <c r="D12" t="n">
-        <v>22.32023521300155</v>
+        <v>29.76881950520252</v>
       </c>
       <c r="E12" t="n">
-        <v>8.201316595077515</v>
+        <v>8.00915002822876</v>
       </c>
       <c r="F12" t="n">
-        <v>213.8243958950043</v>
+        <v>231.884213924408</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -742,22 +742,22 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.6997432578051653</v>
+        <v>0.8585918641166462</v>
       </c>
       <c r="B13" t="n">
-        <v>22.12996973961071</v>
+        <v>31.05583508142715</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7256725502193061</v>
+        <v>0.8862442031651865</v>
       </c>
       <c r="D13" t="n">
-        <v>23.01404764322427</v>
+        <v>31.72534472737489</v>
       </c>
       <c r="E13" t="n">
-        <v>8.273212909698486</v>
+        <v>8.156911849975586</v>
       </c>
       <c r="F13" t="n">
-        <v>215.4543795585632</v>
+        <v>231.3602073192596</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -767,22 +767,22 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.653475282256033</v>
+        <v>0.8119725555187114</v>
       </c>
       <c r="B14" t="n">
-        <v>23.65634862641397</v>
+        <v>31.52127469885984</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6913169854224812</v>
+        <v>0.8639783665374731</v>
       </c>
       <c r="D14" t="n">
-        <v>25.04508514599263</v>
+        <v>32.63886601181256</v>
       </c>
       <c r="E14" t="n">
-        <v>8.434528350830078</v>
+        <v>8.187458992004395</v>
       </c>
       <c r="F14" t="n">
-        <v>215.0032088756561</v>
+        <v>230.5898509025574</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -792,22 +792,22 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.6955838565814847</v>
+        <v>0.8428170931923807</v>
       </c>
       <c r="B15" t="n">
-        <v>22.71535747181723</v>
+        <v>30.097421585179</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7129231096322856</v>
+        <v>0.8613901029910731</v>
       </c>
       <c r="D15" t="n">
-        <v>23.40081977743967</v>
+        <v>30.51596280877989</v>
       </c>
       <c r="E15" t="n">
-        <v>8.225948333740234</v>
+        <v>8.011556386947632</v>
       </c>
       <c r="F15" t="n">
-        <v>217.6217019557953</v>
+        <v>232.2734808921814</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -817,22 +817,22 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.6465522938892675</v>
+        <v>0.8254238287835427</v>
       </c>
       <c r="B16" t="n">
-        <v>23.54370043660214</v>
+        <v>31.50206251478359</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6836636591234785</v>
+        <v>0.8583724453283536</v>
       </c>
       <c r="D16" t="n">
-        <v>24.77250240572955</v>
+        <v>32.1993056205572</v>
       </c>
       <c r="E16" t="n">
-        <v>8.192989349365234</v>
+        <v>7.997745513916016</v>
       </c>
       <c r="F16" t="n">
-        <v>217.4734542369843</v>
+        <v>233.2043614387512</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -842,22 +842,22 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.6701332365494406</v>
+        <v>0.8292301951109501</v>
       </c>
       <c r="B17" t="n">
-        <v>23.96825649196391</v>
+        <v>30.89494226708016</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7024000077786021</v>
+        <v>0.8482906225420133</v>
       </c>
       <c r="D17" t="n">
-        <v>25.02785658094865</v>
+        <v>31.27627633569444</v>
       </c>
       <c r="E17" t="n">
-        <v>8.218839883804321</v>
+        <v>8.058387756347656</v>
       </c>
       <c r="F17" t="n">
-        <v>221.4938471317291</v>
+        <v>236.4462993144989</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -867,22 +867,22 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0.6422650037335457</v>
+        <v>0.8838390401035351</v>
       </c>
       <c r="B18" t="n">
-        <v>23.79447490363515</v>
+        <v>34.65552479897326</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6954067589794886</v>
+        <v>0.9001278738320978</v>
       </c>
       <c r="D18" t="n">
-        <v>25.64228042003837</v>
+        <v>35.70983106475759</v>
       </c>
       <c r="E18" t="n">
-        <v>8.192787408828735</v>
+        <v>8.029119968414307</v>
       </c>
       <c r="F18" t="n">
-        <v>221.8945744037628</v>
+        <v>233.6878912448883</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -892,22 +892,22 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0.6427247675945349</v>
+        <v>0.8399462214682732</v>
       </c>
       <c r="B19" t="n">
-        <v>23.57638458201959</v>
+        <v>32.34557948793783</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6836776561610795</v>
+        <v>0.8683236873782544</v>
       </c>
       <c r="D19" t="n">
-        <v>24.91222385314426</v>
+        <v>33.1843597795318</v>
       </c>
       <c r="E19" t="n">
-        <v>8.223787307739258</v>
+        <v>8.000216245651245</v>
       </c>
       <c r="F19" t="n">
-        <v>220.6141557693481</v>
+        <v>233.15882396698</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -917,22 +917,22 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0.6494281478560346</v>
+        <v>0.8655264292725889</v>
       </c>
       <c r="B20" t="n">
-        <v>24.23052780960694</v>
+        <v>34.26336694205748</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7002073009194622</v>
+        <v>0.8828284455881562</v>
       </c>
       <c r="D20" t="n">
-        <v>25.83824537913726</v>
+        <v>35.11503831916588</v>
       </c>
       <c r="E20" t="n">
-        <v>8.23316216468811</v>
+        <v>8.025230407714844</v>
       </c>
       <c r="F20" t="n">
-        <v>223.1190533638</v>
+        <v>233.8842072486877</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -942,22 +942,22 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0.6252230638144356</v>
+        <v>0.7987763416065312</v>
       </c>
       <c r="B21" t="n">
-        <v>23.98459345129258</v>
+        <v>32.01023515523241</v>
       </c>
       <c r="C21" t="n">
-        <v>0.6642629536412338</v>
+        <v>0.8527556356544118</v>
       </c>
       <c r="D21" t="n">
-        <v>25.42788450333855</v>
+        <v>33.26707051453334</v>
       </c>
       <c r="E21" t="n">
-        <v>8.441623687744141</v>
+        <v>7.989810228347778</v>
       </c>
       <c r="F21" t="n">
-        <v>217.9644474983215</v>
+        <v>232.0362684726715</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -967,22 +967,22 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0.6519943193614361</v>
+        <v>0.896199740652927</v>
       </c>
       <c r="B22" t="n">
-        <v>23.46377967178262</v>
+        <v>34.59005306281427</v>
       </c>
       <c r="C22" t="n">
-        <v>0.697566214930101</v>
+        <v>0.8982390848452383</v>
       </c>
       <c r="D22" t="n">
-        <v>25.09724728901909</v>
+        <v>35.08155826466881</v>
       </c>
       <c r="E22" t="n">
-        <v>8.213945388793945</v>
+        <v>8.18741512298584</v>
       </c>
       <c r="F22" t="n">
-        <v>221.3091490268707</v>
+        <v>234.2646508216858</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -992,22 +992,22 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>0.64450660838993</v>
+        <v>0.8298612228794274</v>
       </c>
       <c r="B23" t="n">
-        <v>23.92905088715562</v>
+        <v>32.43234230962</v>
       </c>
       <c r="C23" t="n">
-        <v>0.6859640502865983</v>
+        <v>0.8624353650597671</v>
       </c>
       <c r="D23" t="n">
-        <v>25.27713786143339</v>
+        <v>33.22379605934579</v>
       </c>
       <c r="E23" t="n">
-        <v>8.189152002334595</v>
+        <v>8.118601083755493</v>
       </c>
       <c r="F23" t="n">
-        <v>220.4271910190582</v>
+        <v>232.3746535778046</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1017,22 +1017,22 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>0.7179242419541865</v>
+        <v>0.8206149667905466</v>
       </c>
       <c r="B24" t="n">
-        <v>21.75266889718875</v>
+        <v>28.69376188806088</v>
       </c>
       <c r="C24" t="n">
-        <v>0.725110053938563</v>
+        <v>0.8479198203283584</v>
       </c>
       <c r="D24" t="n">
-        <v>22.2768059796795</v>
+        <v>29.19798126382335</v>
       </c>
       <c r="E24" t="n">
-        <v>8.264315128326416</v>
+        <v>7.993441343307495</v>
       </c>
       <c r="F24" t="n">
-        <v>214.6569695472717</v>
+        <v>232.5244007110596</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1042,22 +1042,22 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0.6563346318103077</v>
+        <v>0.8442477324365184</v>
       </c>
       <c r="B25" t="n">
-        <v>23.0408606869528</v>
+        <v>32.24000764346942</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7004683943124035</v>
+        <v>0.8817902830998645</v>
       </c>
       <c r="D25" t="n">
-        <v>24.33333658240537</v>
+        <v>33.24461993800993</v>
       </c>
       <c r="E25" t="n">
-        <v>8.209778785705566</v>
+        <v>7.96843433380127</v>
       </c>
       <c r="F25" t="n">
-        <v>219.3673295974731</v>
+        <v>232.6283111572266</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>0.6569758063375104</v>
+        <v>0.8035996073989897</v>
       </c>
       <c r="B26" t="n">
-        <v>22.44829126622022</v>
+        <v>30.57259191470457</v>
       </c>
       <c r="C26" t="n">
-        <v>0.6801866321924589</v>
+        <v>0.8477878048720986</v>
       </c>
       <c r="D26" t="n">
-        <v>23.39366011607758</v>
+        <v>31.31077984073757</v>
       </c>
       <c r="E26" t="n">
-        <v>8.191428899765015</v>
+        <v>8.242789745330811</v>
       </c>
       <c r="F26" t="n">
-        <v>216.5016891956329</v>
+        <v>232.1562716960907</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1092,22 +1092,22 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0.7584909832260907</v>
+        <v>0.8568970895908777</v>
       </c>
       <c r="B27" t="n">
-        <v>21.86559517064057</v>
+        <v>28.85714783883179</v>
       </c>
       <c r="C27" t="n">
-        <v>0.7603832387701521</v>
+        <v>0.8672107937247505</v>
       </c>
       <c r="D27" t="n">
-        <v>22.18453237639881</v>
+        <v>29.00272685130198</v>
       </c>
       <c r="E27" t="n">
-        <v>8.275417566299438</v>
+        <v>8.589110612869263</v>
       </c>
       <c r="F27" t="n">
-        <v>214.8788268566132</v>
+        <v>234.7915799617767</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1117,22 +1117,22 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0.7104282955590132</v>
+        <v>0.772146060334223</v>
       </c>
       <c r="B28" t="n">
-        <v>21.90559474093139</v>
+        <v>30.09366594780745</v>
       </c>
       <c r="C28" t="n">
-        <v>0.7210033438094302</v>
+        <v>0.7975129173506282</v>
       </c>
       <c r="D28" t="n">
-        <v>22.54098296393089</v>
+        <v>30.63808399944175</v>
       </c>
       <c r="E28" t="n">
-        <v>8.197750806808472</v>
+        <v>7.970597743988037</v>
       </c>
       <c r="F28" t="n">
-        <v>208.0587248802185</v>
+        <v>233.2827317714691</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1142,22 +1142,22 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0.648540739272944</v>
+        <v>0.7831620151250025</v>
       </c>
       <c r="B29" t="n">
-        <v>22.9366538251913</v>
+        <v>30.4942851316619</v>
       </c>
       <c r="C29" t="n">
-        <v>0.678224792909367</v>
+        <v>0.8382439462062398</v>
       </c>
       <c r="D29" t="n">
-        <v>23.98970349491675</v>
+        <v>31.36926054704979</v>
       </c>
       <c r="E29" t="n">
-        <v>8.177375316619873</v>
+        <v>7.961889266967773</v>
       </c>
       <c r="F29" t="n">
-        <v>214.6708035469055</v>
+        <v>231.285649061203</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1167,22 +1167,22 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>0.691742369494997</v>
+        <v>0.8417416276127211</v>
       </c>
       <c r="B30" t="n">
-        <v>22.18418374392559</v>
+        <v>30.05797467244515</v>
       </c>
       <c r="C30" t="n">
-        <v>0.7122474496038387</v>
+        <v>0.8737100380742908</v>
       </c>
       <c r="D30" t="n">
-        <v>23.00338515084626</v>
+        <v>30.69668920868422</v>
       </c>
       <c r="E30" t="n">
-        <v>8.21558666229248</v>
+        <v>8.42449164390564</v>
       </c>
       <c r="F30" t="n">
-        <v>213.1496276855469</v>
+        <v>230.0867328643799</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1192,22 +1192,22 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>0.6857703799879854</v>
+        <v>0.8624043533888642</v>
       </c>
       <c r="B31" t="n">
-        <v>23.8043066205252</v>
+        <v>32.21075256460959</v>
       </c>
       <c r="C31" t="n">
-        <v>0.7200437452260916</v>
+        <v>0.8802344247018575</v>
       </c>
       <c r="D31" t="n">
-        <v>25.06407504158438</v>
+        <v>32.78250423313218</v>
       </c>
       <c r="E31" t="n">
-        <v>8.215043783187866</v>
+        <v>7.979468584060669</v>
       </c>
       <c r="F31" t="n">
-        <v>216.4677691459656</v>
+        <v>231.1998076438904</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1217,22 +1217,22 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0.7068694858716188</v>
+        <v>0.8611573995189865</v>
       </c>
       <c r="B32" t="n">
-        <v>22.12014907341231</v>
+        <v>30.56760603495666</v>
       </c>
       <c r="C32" t="n">
-        <v>0.733828521856188</v>
+        <v>0.8946597381081375</v>
       </c>
       <c r="D32" t="n">
-        <v>22.99413234514211</v>
+        <v>31.28893133021144</v>
       </c>
       <c r="E32" t="n">
-        <v>8.187978982925415</v>
+        <v>7.986481904983521</v>
       </c>
       <c r="F32" t="n">
-        <v>212.610419511795</v>
+        <v>227.267612695694</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1242,22 +1242,22 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>0.6154082522723705</v>
+        <v>0.7266579388517764</v>
       </c>
       <c r="B33" t="n">
-        <v>23.10256381653963</v>
+        <v>29.63909542248976</v>
       </c>
       <c r="C33" t="n">
-        <v>0.6410408176933432</v>
+        <v>0.7971810864473126</v>
       </c>
       <c r="D33" t="n">
-        <v>24.16158149246014</v>
+        <v>30.55901286776243</v>
       </c>
       <c r="E33" t="n">
-        <v>8.25638222694397</v>
+        <v>7.973519325256348</v>
       </c>
       <c r="F33" t="n">
-        <v>217.559595823288</v>
+        <v>233.5384283065796</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1267,22 +1267,22 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0.665476480112918</v>
+        <v>0.8550567970942243</v>
       </c>
       <c r="B34" t="n">
-        <v>23.75204033882435</v>
+        <v>32.1237866766658</v>
       </c>
       <c r="C34" t="n">
-        <v>0.7056213672787426</v>
+        <v>0.8819762132894668</v>
       </c>
       <c r="D34" t="n">
-        <v>25.13744644928545</v>
+        <v>32.93731793875205</v>
       </c>
       <c r="E34" t="n">
-        <v>8.18601655960083</v>
+        <v>8.074136972427368</v>
       </c>
       <c r="F34" t="n">
-        <v>218.0663788318634</v>
+        <v>231.6506772041321</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1292,22 +1292,22 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>0.6544493367212184</v>
+        <v>0.8811415972110648</v>
       </c>
       <c r="B35" t="n">
-        <v>23.86237928841918</v>
+        <v>33.52401762565798</v>
       </c>
       <c r="C35" t="n">
-        <v>0.6995569419539369</v>
+        <v>0.888461526941112</v>
       </c>
       <c r="D35" t="n">
-        <v>25.45845888290954</v>
+        <v>33.99388576763451</v>
       </c>
       <c r="E35" t="n">
-        <v>8.180566072463989</v>
+        <v>7.987284183502197</v>
       </c>
       <c r="F35" t="n">
-        <v>221.7712028026581</v>
+        <v>234.170923948288</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1317,22 +1317,22 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>0.6374725543368124</v>
+        <v>0.8103620954393543</v>
       </c>
       <c r="B36" t="n">
-        <v>23.41534761696942</v>
+        <v>31.49148543267308</v>
       </c>
       <c r="C36" t="n">
-        <v>0.6758783926743155</v>
+        <v>0.8590287480960895</v>
       </c>
       <c r="D36" t="n">
-        <v>24.77822733895757</v>
+        <v>32.62020952403121</v>
       </c>
       <c r="E36" t="n">
-        <v>8.19678521156311</v>
+        <v>7.968945503234863</v>
       </c>
       <c r="F36" t="n">
-        <v>217.7311551570892</v>
+        <v>232.2294969558716</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1342,22 +1342,22 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>0.6191586056096147</v>
+        <v>0.8022884224288618</v>
       </c>
       <c r="B37" t="n">
-        <v>24.84181726635215</v>
+        <v>32.57330860193332</v>
       </c>
       <c r="C37" t="n">
-        <v>0.6614251876581574</v>
+        <v>0.8536036650547421</v>
       </c>
       <c r="D37" t="n">
-        <v>26.59280412910282</v>
+        <v>33.99678622442047</v>
       </c>
       <c r="E37" t="n">
-        <v>8.453846454620361</v>
+        <v>8.002221345901489</v>
       </c>
       <c r="F37" t="n">
-        <v>217.2351207733154</v>
+        <v>233.4948830604553</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1367,22 +1367,22 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0.6821299182497229</v>
+        <v>0.84658263588782</v>
       </c>
       <c r="B38" t="n">
-        <v>23.64243069238789</v>
+        <v>31.84671511869504</v>
       </c>
       <c r="C38" t="n">
-        <v>0.7184700284171629</v>
+        <v>0.8873005617613682</v>
       </c>
       <c r="D38" t="n">
-        <v>24.85882526770689</v>
+        <v>32.95435451920219</v>
       </c>
       <c r="E38" t="n">
-        <v>8.208329677581787</v>
+        <v>8.761768817901611</v>
       </c>
       <c r="F38" t="n">
-        <v>212.7799324989319</v>
+        <v>231.2552201747894</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1392,22 +1392,22 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>0.6742817306802672</v>
+        <v>0.8392720072379181</v>
       </c>
       <c r="B39" t="n">
-        <v>23.76657725864191</v>
+        <v>31.66645341681736</v>
       </c>
       <c r="C39" t="n">
-        <v>0.7103652905568473</v>
+        <v>0.8731530690736338</v>
       </c>
       <c r="D39" t="n">
-        <v>25.02314653847163</v>
+        <v>32.49990469483676</v>
       </c>
       <c r="E39" t="n">
-        <v>8.218409299850464</v>
+        <v>8.347167491912842</v>
       </c>
       <c r="F39" t="n">
-        <v>214.5237097740173</v>
+        <v>232.4011120796204</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1417,22 +1417,22 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0.6962515646246584</v>
+        <v>0.8972539614716862</v>
       </c>
       <c r="B40" t="n">
-        <v>22.80415263482314</v>
+        <v>32.29890506362858</v>
       </c>
       <c r="C40" t="n">
-        <v>0.7312023771714329</v>
+        <v>0.9209732193248567</v>
       </c>
       <c r="D40" t="n">
-        <v>23.98324012224254</v>
+        <v>33.54365820515776</v>
       </c>
       <c r="E40" t="n">
-        <v>8.179183959960938</v>
+        <v>8.037747859954834</v>
       </c>
       <c r="F40" t="n">
-        <v>213.0640215873718</v>
+        <v>231.3639054298401</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1442,22 +1442,22 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>0.8913489432515032</v>
+        <v>0.9629576095908792</v>
       </c>
       <c r="B41" t="n">
-        <v>22.34874102435249</v>
+        <v>28.25322455221523</v>
       </c>
       <c r="C41" t="n">
-        <v>0.8904893659830628</v>
+        <v>0.9628089687755996</v>
       </c>
       <c r="D41" t="n">
-        <v>22.37656288672884</v>
+        <v>28.4222493376752</v>
       </c>
       <c r="E41" t="n">
-        <v>8.210419416427612</v>
+        <v>7.98309850692749</v>
       </c>
       <c r="F41" t="n">
-        <v>209.8459489345551</v>
+        <v>232.2623732089996</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1467,22 +1467,22 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>0.6768229992275205</v>
+        <v>0.8503603843892731</v>
       </c>
       <c r="B42" t="n">
-        <v>22.87890979960353</v>
+        <v>31.43251970710911</v>
       </c>
       <c r="C42" t="n">
-        <v>0.7051742812317159</v>
+        <v>0.8697801574720092</v>
       </c>
       <c r="D42" t="n">
-        <v>23.90159972633661</v>
+        <v>32.20192202887067</v>
       </c>
       <c r="E42" t="n">
-        <v>8.231444835662842</v>
+        <v>8.066930770874023</v>
       </c>
       <c r="F42" t="n">
-        <v>212.6665666103363</v>
+        <v>231.5367991924286</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1492,22 +1492,22 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>0.7323154935704573</v>
+        <v>0.8624390194118247</v>
       </c>
       <c r="B43" t="n">
-        <v>22.7024568685691</v>
+        <v>29.70871756567172</v>
       </c>
       <c r="C43" t="n">
-        <v>0.7467680144936095</v>
+        <v>0.8911878238307339</v>
       </c>
       <c r="D43" t="n">
-        <v>23.378802582159</v>
+        <v>30.36046528843861</v>
       </c>
       <c r="E43" t="n">
-        <v>8.207729816436768</v>
+        <v>8.052848815917969</v>
       </c>
       <c r="F43" t="n">
-        <v>212.5161945819855</v>
+        <v>229.7736151218414</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1517,22 +1517,22 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>0.7424010470445611</v>
+        <v>0.8581998159674141</v>
       </c>
       <c r="B44" t="n">
-        <v>22.98073944047153</v>
+        <v>29.3558072963002</v>
       </c>
       <c r="C44" t="n">
-        <v>0.7569281256132709</v>
+        <v>0.8872580484758337</v>
       </c>
       <c r="D44" t="n">
-        <v>23.58531337431398</v>
+        <v>30.00967188848685</v>
       </c>
       <c r="E44" t="n">
-        <v>8.198308229446411</v>
+        <v>7.969984531402588</v>
       </c>
       <c r="F44" t="n">
-        <v>211.5077171325684</v>
+        <v>231.029310464859</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1542,22 +1542,22 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>0.6868808350700172</v>
+        <v>0.8882086004512647</v>
       </c>
       <c r="B45" t="n">
-        <v>23.58861539966775</v>
+        <v>32.74383860555601</v>
       </c>
       <c r="C45" t="n">
-        <v>0.7285033880342077</v>
+        <v>0.9112052732096231</v>
       </c>
       <c r="D45" t="n">
-        <v>25.02552166818016</v>
+        <v>33.85612666565918</v>
       </c>
       <c r="E45" t="n">
-        <v>8.168112754821777</v>
+        <v>7.960805416107178</v>
       </c>
       <c r="F45" t="n">
-        <v>215.100533246994</v>
+        <v>231.8205099105835</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>0.7670755231038109</v>
+        <v>0.9390104154477126</v>
       </c>
       <c r="B46" t="n">
-        <v>22.50211083556506</v>
+        <v>31.42956342035941</v>
       </c>
       <c r="C46" t="n">
-        <v>0.791522402353062</v>
+        <v>0.9483462189103722</v>
       </c>
       <c r="D46" t="n">
-        <v>23.14921003504688</v>
+        <v>31.74007118906747</v>
       </c>
       <c r="E46" t="n">
-        <v>8.207495927810669</v>
+        <v>7.980819225311279</v>
       </c>
       <c r="F46" t="n">
-        <v>206.3373446464539</v>
+        <v>234.3986921310425</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -1592,22 +1592,22 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>0.6545652240413612</v>
+        <v>0.8467411321990097</v>
       </c>
       <c r="B47" t="n">
-        <v>23.32302468971005</v>
+        <v>31.81107010232033</v>
       </c>
       <c r="C47" t="n">
-        <v>0.6928455755473382</v>
+        <v>0.8910598665668396</v>
       </c>
       <c r="D47" t="n">
-        <v>24.70906527718645</v>
+        <v>33.20061496725437</v>
       </c>
       <c r="E47" t="n">
-        <v>8.248583078384399</v>
+        <v>7.997151374816895</v>
       </c>
       <c r="F47" t="n">
-        <v>218.2619934082031</v>
+        <v>229.8679249286652</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -1617,22 +1617,22 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>0.699098187603871</v>
+        <v>0.8805208347781283</v>
       </c>
       <c r="B48" t="n">
-        <v>22.64802131745686</v>
+        <v>31.34821463432274</v>
       </c>
       <c r="C48" t="n">
-        <v>0.7250295812925762</v>
+        <v>0.8912202107063875</v>
       </c>
       <c r="D48" t="n">
-        <v>23.49235350571727</v>
+        <v>31.86113648042781</v>
       </c>
       <c r="E48" t="n">
-        <v>8.179736137390137</v>
+        <v>7.955165386199951</v>
       </c>
       <c r="F48" t="n">
-        <v>217.0017635822296</v>
+        <v>232.1981565952301</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -1642,22 +1642,22 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>0.7417712528383466</v>
+        <v>0.8678717072594121</v>
       </c>
       <c r="B49" t="n">
-        <v>22.04622971591921</v>
+        <v>30.36866298712498</v>
       </c>
       <c r="C49" t="n">
-        <v>0.7566372590435037</v>
+        <v>0.8881785800822832</v>
       </c>
       <c r="D49" t="n">
-        <v>22.72642559872914</v>
+        <v>30.99092988931891</v>
       </c>
       <c r="E49" t="n">
-        <v>8.204177856445312</v>
+        <v>7.967688798904419</v>
       </c>
       <c r="F49" t="n">
-        <v>214.1052222251892</v>
+        <v>230.2384927272797</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>0.6410060869070489</v>
+        <v>0.8541385961705518</v>
       </c>
       <c r="B50" t="n">
-        <v>21.99150166359757</v>
+        <v>31.5077742398501</v>
       </c>
       <c r="C50" t="n">
-        <v>0.6762660732622686</v>
+        <v>0.8896322825147743</v>
       </c>
       <c r="D50" t="n">
-        <v>23.30829511293512</v>
+        <v>32.54086620037795</v>
       </c>
       <c r="E50" t="n">
-        <v>8.169302701950073</v>
+        <v>7.98175835609436</v>
       </c>
       <c r="F50" t="n">
-        <v>214.7340078353882</v>
+        <v>232.6814386844635</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -1692,22 +1692,22 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>0.7197854292080348</v>
+        <v>0.894521334967206</v>
       </c>
       <c r="B51" t="n">
-        <v>23.28012648563915</v>
+        <v>31.24660341962141</v>
       </c>
       <c r="C51" t="n">
-        <v>0.7523790224330408</v>
+        <v>0.9069281905361051</v>
       </c>
       <c r="D51" t="n">
-        <v>24.24943421015519</v>
+        <v>31.75257761857141</v>
       </c>
       <c r="E51" t="n">
-        <v>8.252106189727783</v>
+        <v>7.969155311584473</v>
       </c>
       <c r="F51" t="n">
-        <v>217.2733373641968</v>
+        <v>232.1581740379333</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
